--- a/output/pdf_financials_xlsx/ENEV.xlsx
+++ b/output/pdf_financials_xlsx/ENEV.xlsx
@@ -1376,16 +1376,16 @@
         <v>-0.393814</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.5764899999999999</v>
+        <v>-0.5764899999999999</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.765866</v>
+        <v>-0.765866</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.237369</v>
+        <v>-0.237369</v>
       </c>
     </row>
     <row r="17">
@@ -1690,16 +1690,16 @@
         <v>-0.393814</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.5764899999999999</v>
+        <v>-0.5764899999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.765866</v>
+        <v>-0.765866</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.237369</v>
+        <v>-0.237369</v>
       </c>
     </row>
     <row r="21">
@@ -1880,16 +1880,16 @@
         <v>-0.393814</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.5764899999999999</v>
+        <v>-0.5764899999999999</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.765866</v>
+        <v>-0.765866</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.237369</v>
+        <v>-0.237369</v>
       </c>
     </row>
     <row r="24">
@@ -2196,16 +2196,16 @@
         <v>-0.393814</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.5764899999999999</v>
+        <v>-0.5764899999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.765866</v>
+        <v>-0.765866</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.237369</v>
+        <v>-0.237369</v>
       </c>
     </row>
     <row r="28">
@@ -2326,16 +2326,16 @@
         <v>-0.359243</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.612391</v>
+        <v>-0.540589</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.799164</v>
+        <v>-0.732568</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.237369</v>
+        <v>-0.237369</v>
       </c>
     </row>
     <row r="30">
@@ -2486,16 +2486,16 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6187,13 +6187,13 @@
         <v>0</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.003828</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.039987</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.055122</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>0</v>
@@ -6223,25 +6223,25 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.2331</v>
+        <v>0.42094</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.42094</v>
+        <v>0.5470739999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.42094</v>
+        <v>0.620459</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.5470739999999999</v>
+        <v>0.666314</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.62388</v>
+        <v>0.6873089999999999</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>1.31343</v>
+        <v>1.383532</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.360746</v>
+        <v>1.451509</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>1.427502</v>
@@ -13794,7 +13794,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -16289,7 +16293,11 @@
           <t>RESERVE FOR WARRANTS (note 9 (b))</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17067,7 +17075,11 @@
           <t>RESERVE FOR WARRANTS (note 9 (b))</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -22239,7 +22251,11 @@
           <t>RESERVE FOR WARRANTS (note 10 (c)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -45955,16 +45971,16 @@
         </is>
       </c>
       <c r="R369" s="5" t="n">
-        <v>0.5764899999999999</v>
+        <v>-0.5764899999999999</v>
       </c>
       <c r="S369" s="5" t="n">
-        <v>0.765866</v>
+        <v>-0.765866</v>
       </c>
       <c r="T369" s="5" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="U369" s="5" t="n">
-        <v>0.237369</v>
+        <v>-0.237369</v>
       </c>
     </row>
     <row r="370">
@@ -46754,10 +46770,10 @@
         </is>
       </c>
       <c r="S377" s="5" t="n">
-        <v>0.765866</v>
+        <v>-0.765866</v>
       </c>
       <c r="T377" s="5" t="n">
-        <v>0.380256</v>
+        <v>-0.380256</v>
       </c>
       <c r="U377" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ENEV.xlsx
+++ b/output/pdf_financials_xlsx/ENEV.xlsx
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000684</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5.8e-05</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000273</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.281835</v>
+        <v>0.281562</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.416876</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.281835</v>
+        <v>0.281562</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.416876</v>
@@ -2609,34 +2609,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.053072</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.055348</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.105854</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.058735</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.045406</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003165</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07704900000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.023371</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.011636</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010188</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.001652</v>
@@ -2648,13 +2648,13 @@
         <v>0.027617</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001764</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000976</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.003043</v>
       </c>
     </row>
     <row r="35">
@@ -2729,34 +2729,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.053072</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.055348</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.105854</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.058735</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.045406</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003165</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07704900000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.023371</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.011636</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010188</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.001652</v>
@@ -2768,13 +2768,13 @@
         <v>0.027617</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001764</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000976</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.003043</v>
       </c>
     </row>
     <row r="37">
@@ -3449,34 +3449,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.116994</v>
+        <v>0.06392200000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.050664</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.144191</v>
+        <v>0.038337</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.070937</v>
+        <v>0.012202</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.082951</v>
+        <v>0.037545</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.003165</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.07704900000000001</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.023371</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.07290199999999999</v>
+        <v>0.061266</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.048309</v>
+        <v>0.038121</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.014173</v>
@@ -3488,7 +3488,7 @@
         <v>0.016199</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.035112</v>
+        <v>0.033348</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -64642,7 +64642,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -67852,7 +67852,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
